--- a/interviews/interviews/Prepare for interview.xlsx
+++ b/interviews/interviews/Prepare for interview.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chaadal\interviews\interviews\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chaadal\EverythingInterviews\interviews\interviews\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8984047D-C316-41AD-AA5A-52AF546C74B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844B3933-4EAF-4C76-AFF8-F6AF14D26851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Link</t>
   </si>
@@ -172,6 +172,45 @@
   </si>
   <si>
     <t>ACID properties in DBMS</t>
+  </si>
+  <si>
+    <t>Idempotency</t>
+  </si>
+  <si>
+    <t>https://medium.com/@reetesh043/rest-api-design-what-is-idempotency-18218e1ff73c</t>
+  </si>
+  <si>
+    <t>Internal working of Hashmaps</t>
+  </si>
+  <si>
+    <t>https://medium.com/@yashodhara.chowkar/internal-working-of-hashmap-in-java-and-performance-improvement-in-java-8-a28ee1660cda</t>
+  </si>
+  <si>
+    <t>ANGULAR</t>
+  </si>
+  <si>
+    <t>https://medium.com/@lquocnam/a-comprehensive-guide-to-angular-observables-bde5542346fc</t>
+  </si>
+  <si>
+    <t>Observables</t>
+  </si>
+  <si>
+    <t>SOLID principles</t>
+  </si>
+  <si>
+    <t>https://medium.com/@cibofdevs/understanding-solid-principles-in-java-with-real-life-examples-d6fe93b0acc2</t>
+  </si>
+  <si>
+    <t>https://www.geeksforgeeks.org/java/association-composition-aggregation-java/</t>
+  </si>
+  <si>
+    <t>Association, aggregation and composition</t>
+  </si>
+  <si>
+    <t>https://medium.com/@vinciabhinav7/concurrency-in-java-executorservice-future-and-callable-f22a7fbeefe2</t>
+  </si>
+  <si>
+    <t>Executor Service, Future and Callable</t>
   </si>
 </sst>
 </file>
@@ -536,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.7109375" style="1" customWidth="1"/>
@@ -737,6 +776,59 @@
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -760,6 +852,12 @@
     <hyperlink ref="B19" r:id="rId17" xr:uid="{A9E6E3FD-1734-4B13-BC33-BF2408368848}"/>
     <hyperlink ref="B21" r:id="rId18" xr:uid="{B68A4330-6652-439B-AE1F-AF7AA4A9CADD}"/>
     <hyperlink ref="B22" r:id="rId19" xr:uid="{1E1BF8A4-D0A9-4564-9D96-B42605015528}"/>
+    <hyperlink ref="B24" r:id="rId20" xr:uid="{0AC2E1FC-B85B-4411-AFC0-30CAC8170EA5}"/>
+    <hyperlink ref="B25" r:id="rId21" xr:uid="{AF694210-4CB7-489A-B7E0-DC7C3BBB17EC}"/>
+    <hyperlink ref="B101" r:id="rId22" xr:uid="{88B1C501-7002-41F4-8AB2-985E971A15EE}"/>
+    <hyperlink ref="B26" r:id="rId23" xr:uid="{57C4949F-BA58-4240-9CCE-BBACCF442008}"/>
+    <hyperlink ref="B27" r:id="rId24" xr:uid="{94D92D4A-E0F6-4989-B8AA-FE6FFBDA702F}"/>
+    <hyperlink ref="B28" r:id="rId25" xr:uid="{32430468-2174-4CBE-80A6-2C5BABC9DD61}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/interviews/interviews/Prepare for interview.xlsx
+++ b/interviews/interviews/Prepare for interview.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chaadal\EverythingInterviews\interviews\interviews\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844B3933-4EAF-4C76-AFF8-F6AF14D26851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C50C212-247E-4347-A686-86DB7D6AE0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Link</t>
   </si>
@@ -211,6 +211,12 @@
   </si>
   <si>
     <t>Executor Service, Future and Callable</t>
+  </si>
+  <si>
+    <t>Java Flight Recorder</t>
+  </si>
+  <si>
+    <t>https://www.baeldung.com/java-flight-recorder-monitoring</t>
   </si>
 </sst>
 </file>
@@ -818,6 +824,14 @@
         <v>60</v>
       </c>
     </row>
+    <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>53</v>
@@ -858,6 +872,7 @@
     <hyperlink ref="B26" r:id="rId23" xr:uid="{57C4949F-BA58-4240-9CCE-BBACCF442008}"/>
     <hyperlink ref="B27" r:id="rId24" xr:uid="{94D92D4A-E0F6-4989-B8AA-FE6FFBDA702F}"/>
     <hyperlink ref="B28" r:id="rId25" xr:uid="{32430468-2174-4CBE-80A6-2C5BABC9DD61}"/>
+    <hyperlink ref="B29" r:id="rId26" xr:uid="{0130B59E-D72F-49BA-9170-66569FB05BC8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
